--- a/artfynd/A 34146-2023 artfynd.xlsx
+++ b/artfynd/A 34146-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34146-2023 artfynd.xlsx
+++ b/artfynd/A 34146-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111897598</v>
+        <v>111897600</v>
       </c>
       <c r="B2" t="n">
-        <v>89517</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>882943</v>
+        <v>882516</v>
       </c>
       <c r="R2" t="n">
-        <v>7398198</v>
+        <v>7398025</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,50 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111897597</v>
+        <v>111897797</v>
       </c>
       <c r="B3" t="n">
-        <v>89517</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lammivaara, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>882561</v>
+        <v>882378</v>
       </c>
       <c r="R3" t="n">
-        <v>7398041</v>
+        <v>7397974</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -861,6 +854,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -879,15 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111897599</v>
+        <v>111897597</v>
       </c>
       <c r="B4" t="n">
-        <v>89517</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>883002</v>
+        <v>882560</v>
       </c>
       <c r="R4" t="n">
-        <v>7398231</v>
+        <v>7398040</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,37 +970,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111897600</v>
+        <v>111897598</v>
       </c>
       <c r="B5" t="n">
-        <v>89553</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>882516</v>
+        <v>882943</v>
       </c>
       <c r="R5" t="n">
-        <v>7398025</v>
+        <v>7398198</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,53 +1067,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111897797</v>
+        <v>111897599</v>
       </c>
       <c r="B6" t="n">
-        <v>81385</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lammivaara, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>882379</v>
+        <v>883002</v>
       </c>
       <c r="R6" t="n">
-        <v>7397974</v>
+        <v>7398231</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1170,7 +1146,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1189,15 +1164,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111897604</v>
+        <v>111897607</v>
       </c>
       <c r="B7" t="n">
-        <v>96735</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1205,21 +1175,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1229,10 +1199,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>882944</v>
+        <v>882630</v>
       </c>
       <c r="R7" t="n">
-        <v>7398200</v>
+        <v>7398035</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1291,37 +1261,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111897605</v>
+        <v>111897608</v>
       </c>
       <c r="B8" t="n">
-        <v>89571</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1331,10 +1296,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>882939</v>
+        <v>882666</v>
       </c>
       <c r="R8" t="n">
-        <v>7398180</v>
+        <v>7398058</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1393,37 +1358,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111897601</v>
+        <v>111897610</v>
       </c>
       <c r="B9" t="n">
-        <v>78740</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1393,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>882279</v>
+        <v>882792</v>
       </c>
       <c r="R9" t="n">
-        <v>7397923</v>
+        <v>7398101</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1495,19 +1455,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111897612</v>
+        <v>111897611</v>
       </c>
       <c r="B10" t="n">
-        <v>77650</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1535,10 +1490,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>882946</v>
+        <v>882789</v>
       </c>
       <c r="R10" t="n">
-        <v>7398206</v>
+        <v>7398099</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1597,53 +1552,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111897860</v>
+        <v>111897612</v>
       </c>
       <c r="B11" t="n">
-        <v>78647</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lammivaara, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>882955</v>
+        <v>882945</v>
       </c>
       <c r="R11" t="n">
-        <v>7398199</v>
+        <v>7398206</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1684,7 +1631,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1700,6 +1646,504 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>111897860</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>882955</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7398198</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>111897602</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80460</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>882837</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7398124</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>111897601</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>882279</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7397923</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>111897939</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>882419</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7397968</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Hackspår i träd</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>111897604</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>882944</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7398199</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34146-2023 artfynd.xlsx
+++ b/artfynd/A 34146-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111897600</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111897797</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111897597</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111897598</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111897599</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111897607</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,6 +1390,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111897608</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1452,6 +1492,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111897610</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1549,6 +1594,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111897611</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1646,6 +1696,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111897612</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1747,6 +1802,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111897860</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1844,6 +1904,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111897602</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1941,6 +2006,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111897601</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2047,6 +2117,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111897939</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2144,8 +2219,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111897604</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>